--- a/Result/profitability/1723.xlsx
+++ b/Result/profitability/1723.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>1.79</v>
       </c>
       <c r="M2" t="n">
-        <v>0.9650000000000001</v>
+        <v>0.9425</v>
       </c>
       <c r="N2" t="n">
-        <v>22.2475</v>
+        <v>21.98125</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>1.81</v>
       </c>
       <c r="M3" t="n">
-        <v>1.00625</v>
+        <v>1.04</v>
       </c>
       <c r="N3" t="n">
-        <v>21.8175</v>
+        <v>21.95</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>1.8</v>
       </c>
       <c r="M4" t="n">
-        <v>1.1025</v>
+        <v>1.1475</v>
       </c>
       <c r="N4" t="n">
-        <v>21.8275</v>
+        <v>21.8875</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>1.08</v>
       </c>
       <c r="M5" t="n">
-        <v>1.12</v>
+        <v>1.19875</v>
       </c>
       <c r="N5" t="n">
-        <v>21.5875</v>
+        <v>22.19375</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -1137,10 +1137,10 @@
         <v>0.92</v>
       </c>
       <c r="M6" t="n">
-        <v>1.15125</v>
+        <v>1.2475</v>
       </c>
       <c r="N6" t="n">
-        <v>22.7325</v>
+        <v>23.36875</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>1.49</v>
       </c>
       <c r="M7" t="n">
-        <v>1.27125</v>
+        <v>1.37</v>
       </c>
       <c r="N7" t="n">
-        <v>24.65</v>
+        <v>25.29</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>1.64</v>
       </c>
       <c r="M8" t="n">
-        <v>1.4125</v>
+        <v>1.47875</v>
       </c>
       <c r="N8" t="n">
-        <v>26.5475</v>
+        <v>26.2575</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>1723</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>2043</v>
+      </c>
+      <c r="D75" t="n">
+        <v>1581</v>
+      </c>
+      <c r="E75" t="n">
+        <v>462</v>
+      </c>
+      <c r="F75" t="n">
+        <v>22.61</v>
+      </c>
+      <c r="G75" t="n">
+        <v>304</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>14.88%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>40</v>
+      </c>
+      <c r="J75" t="n">
+        <v>344</v>
+      </c>
+      <c r="K75" t="n">
+        <v>302</v>
+      </c>
+      <c r="L75" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.9037500000000001</v>
+      </c>
+      <c r="N75" t="n">
+        <v>21.09125</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.6883116883116884</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-2.32</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.09306056959486564</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>0.9402985074626866</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>4.849999999999998</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.2730855855855854</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
